--- a/data/codebook/Q15.xlsx
+++ b/data/codebook/Q15.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PT-BR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EN-US" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -567,7 +567,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -599,7 +599,7 @@
       <c r="Z1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Q15: Based on your experience, how do you balance different data quality characteristics, such as accuracy, comprehensibility and computational efficiency, when
 developing machine learning-enabled systems? </t>
@@ -660,32 +660,32 @@
       <c r="Z3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Sub categoria</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Quote</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>Resposta</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -712,23 +712,23 @@
       <c r="Z4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>TRADE-OFFS E TENSÕES INERENTES</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Sacrifício da precisão pela viabilidade computacional</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>Equilibrar precisão, compreensibilidade e eficiência computacional exige escolhas estratégicas</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>Equilibrar precisão, compreensibilidade e eficiência computacional exige escolhas estratégicas. Para modelos críticos, como risco de crédito, priorizamos interpretabilidade (árvores de decisão). Em visão computacional móvel, sacrificamos um pouco de precisão por eficiência (MobileNet). Já em detecção de fraudes, combinamos regras simples (rápidas e explicáveis) com machine learning sofisticado.</t>
         </is>
@@ -760,23 +760,23 @@
       <c r="Z5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>HIERARQUIZAÇÃO EXPLÍCITA DE CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Precisão como prioridade máxima</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">A prioridade é na precisão dos dados, seguido de compreensibilidade e eficiência </t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">A prioridade é na precisão dos dados, seguido de compreensibilidade e eficiência </t>
         </is>
@@ -808,23 +808,23 @@
       <c r="Z6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Tudo vai depender de como nossa aplicação precisará responder ao usuário </t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Tudo vai depender de como nossa aplicação precisará responder ao usuário </t>
         </is>
@@ -856,23 +856,23 @@
       <c r="Z7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>Equilibrar precisão, compreensibilidade e eficiência computacional no desenvolvimento de sistemas de aprendizado de máquina exige decisões estratégicas que dependem do contexto do projeto.</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Equilibrar precisão, compreensibilidade e eficiência computacional no desenvolvimento de sistemas de aprendizado de máquina exige decisões estratégicas que dependem do contexto do projeto.</t>
         </is>
@@ -904,23 +904,23 @@
       <c r="Z8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Escolha do modelo conforme prioridade</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Modelos mais simples podem ser preferíveis quando a explicabilidade é essencial, enquanto modelos complexos são escolhidos quando a precisão é prioridade.</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>Equilibrar precisão, compreensibilidade e eficiência computacional em aprendizado de máquina exige priorização baseada no contexto do projeto. Uso técnicas como seleção de features, redução de dimensionalidade e limpeza de dados para manter a representatividade sem comprometer a interpretabilidade. Modelos mais simples podem ser preferíveis quando a explicabilidade é essencial, enquanto modelos complexos são escolhidos quando a precisão é prioridade. Além disso, monitoro continuamente o desempenho do sistema para ajustar esse equilíbrio conforme necessário.</t>
         </is>
@@ -952,23 +952,23 @@
       <c r="Z9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Técnicas de pré-processamento e engenharia de features</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>seleção de features, redução de dimensionalidade e limpeza de dados para manter a representatividade sem comprometer a interpretabilidade</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>Equilibrar precisão, compreensibilidade e eficiência computacional em aprendizado de máquina exige priorização baseada no contexto do projeto. Uso técnicas como seleção de features, redução de dimensionalidade e limpeza de dados para manter a representatividade sem comprometer a interpretabilidade. Modelos mais simples podem ser preferíveis quando a explicabilidade é essencial, enquanto modelos complexos são escolhidos quando a precisão é prioridade. Além disso, monitoro continuamente o desempenho do sistema para ajustar esse equilíbrio conforme necessário.</t>
         </is>
@@ -1000,23 +1000,23 @@
       <c r="Z10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>Equilibrar precisão, compreensibilidade e eficiência computacional em aprendizado de máquina exige priorização baseada no contexto do projeto</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>Equilibrar precisão, compreensibilidade e eficiência computacional em aprendizado de máquina exige priorização baseada no contexto do projeto. Uso técnicas como seleção de features, redução de dimensionalidade e limpeza de dados para manter a representatividade sem comprometer a interpretabilidade. Modelos mais simples podem ser preferíveis quando a explicabilidade é essencial, enquanto modelos complexos são escolhidos quando a precisão é prioridade. Além disso, monitoro continuamente o desempenho do sistema para ajustar esse equilíbrio conforme necessário.</t>
         </is>
@@ -1048,23 +1048,23 @@
       <c r="Z11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Escolha do modelo conforme prioridade</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>ponto ideal entre complexidade e praticidade, garantindo um modelo robusto e utilizável</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>o segredo é encontrar o ponto ideal entre complexidade e praticidade, garantindo um modelo robusto e utilizável</t>
         </is>
@@ -1096,23 +1096,23 @@
       <c r="Z12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>Cada decisão deve ser baseada no contexto específico do projeto e nos objetivos finais, garantindo que a qualidade dos dados seja mantida sem sacrificar outras necessidades críticas.</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>Cada decisão deve ser baseada no contexto específico do projeto e nos objetivos finais, garantindo que a qualidade dos dados seja mantida sem sacrificar outras necessidades críticas.</t>
         </is>
@@ -1144,23 +1144,23 @@
       <c r="Z13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>AUSÊNCIA DE EXPERIÊNCIA OU CONHECIMENTO</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Não-experiência declarada com desenvolvimento de ML</t>
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Não sei descrever </t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Não sei descrever </t>
         </is>
@@ -1192,23 +1192,23 @@
       <c r="Z14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>VALORAÇÃO GERAL DAS CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Reconhecimento da importância universal</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>essenciais para a entrega de valor e resultados eficientes no âmbito da engenharia e análise de dados.</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>Essas características são essenciais para a entrega de valor e resultados eficientes no âmbito da engenharia e análise de dados.</t>
         </is>
@@ -1240,23 +1240,23 @@
       <c r="Z15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>HIERARQUIZAÇÃO EXPLÍCITA DE CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Sequência hierárquica em fases/etapas</t>
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>otimizar o processamento/pipeline tornando melhor a experiência</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>Geralmente o foco se dá inicialmente na qualidade dos dados em termos de serem precisos, completos e atuais. Em um segunda momento pensamos na questão do usuário do sistema e como tornar esse dados mais legíveis. Finalmente, em como otimizar o processamento/pipeline tornando melhor a experiência.</t>
         </is>
@@ -1288,23 +1288,23 @@
       <c r="Z16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>HIERARQUIZAÇÃO EXPLÍCITA DE CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Sequência hierárquica em fases/etapas</t>
         </is>
       </c>
       <c r="C17" s="4" t="n"/>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>usuário do sistema e como tornar esse dados mais legíveis.</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>Geralmente o foco se dá inicialmente na qualidade dos dados em termos de serem precisos, completos e atuais. Em um segunda momento pensamos na questão do usuário do sistema e como tornar esse dados mais legíveis. Finalmente, em como otimizar o processamento/pipeline tornando melhor a experiência.</t>
         </is>
@@ -1336,23 +1336,23 @@
       <c r="Z17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>HIERARQUIZAÇÃO EXPLÍCITA DE CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Sequência hierárquica em fases/etapas</t>
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>foco se dá inicialmente na qualidade dos dados em termos de serem precisos, completos e atuais</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>Geralmente o foco se dá inicialmente na qualidade dos dados em termos de serem precisos, completos e atuais. Em um segunda momento pensamos na questão do usuário do sistema e como tornar esse dados mais legíveis. Finalmente, em como otimizar o processamento/pipeline tornando melhor a experiência.</t>
         </is>
@@ -1384,24 +1384,24 @@
       <c r="Z18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>Trade-offs e Tensões Inerentes</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Aceitação de limitações em troca de credibilidade da fonte
 Índice</t>
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>falta de consistência (no que se refere a possuir contradição entre diferentes fontes) e atualidade (de um ponto de vista geográfico, por não representar a população brasileira) com compreensibilidade (pois são dados que possuem documentação clara), disponibilidade, acessibilidade e principalmente com credibilidade</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>Até agora não participei precisamente do desenvolvimento de um sistema que usa aprendizado de máquina, pois só trabalhei com isso no mestrado. Eu trabalho com imagens médicas, a conciliação que precisei fazer foi basicamente entre a falta de consistência (no que se refere a possuir contradição entre diferentes fontes) e atualidade (de um ponto de vista geográfico, por não representar a população brasileira) com compreensibilidade (pois são dados que possuem documentação clara), disponibilidade, acessibilidade e principalmente com credibilidade, pois são dados disponibilizados por uma agência da Organização das Nações Unidas. E tudo isso será documentado, deixando claro como foi o processo de obter esses dados e como entrar em contato para tal.</t>
         </is>
@@ -1433,23 +1433,23 @@
       <c r="Z19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>AUSÊNCIA DE EXPERIÊNCIA OU CONHECIMENTO</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Não-experiência declarada com desenvolvimento de ML</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>Até agora não participei precisamente do desenvolvimento de um sistema que usa aprendizado de máquina</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>Até agora não participei precisamente do desenvolvimento de um sistema que usa aprendizado de máquina, pois só trabalhei com isso no mestrado. Eu trabalho com imagens médicas, a conciliação que precisei fazer foi basicamente entre a falta de consistência (no que se refere a possuir contradição entre diferentes fontes) e atualidade (de um ponto de vista geográfico, por não representar a população brasileira) com compreensibilidade (pois são dados que possuem documentação clara), disponibilidade, acessibilidade e principalmente com credibilidade, pois são dados disponibilizados por uma agência da Organização das Nações Unidas. E tudo isso será documentado, deixando claro como foi o processo de obter esses dados e como entrar em contato para tal.</t>
         </is>
@@ -1481,23 +1481,23 @@
       <c r="Z20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>HIERARQUIZAÇÃO EXPLÍCITA DE CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Precisão como prioridade máxima</t>
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> mais ênfase na precisão dos dados, seguido da compreensibilidade e eficiência.</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Atualmente sempre venho dando mais ênfase na precisão dos dados, seguido da compreensibilidade e eficiência. Dou prioridade para essa ordem por alguns motivos, o principal deles sendo que (em minhas experiências) quando se utiliza um dataset que não representa dados reais ou realmente representativos do que queremos que os modelos de aprendizado de máquina aprendam o resultado não é satisfatório, a compreensibilidade vem logo em seguida pois facilita tanto o trabalho de ETL (carregar os dados para treinar os modelos) tanto para futura documentação e demonstração dos resultados obtidos pelos modelos, e por fim a eficiência computacional visto que também é preciso manter a capacidade de rodar os modelos com o hardware que for usado. Uma situação que me recordo foi quando estive numa equipe e tivemos que fazer uma escolha entre dois datasets que tinhamos disponíveis para utilizar em um projeto, um deles mais robusto que o outro porém que iria demandar muito mais poder computacional para treinar os modelos em cima dele, no fim acabamos escolhendo ele por representar melhor o tipo de dado que queriamos apresentar no final do projeto. </t>
         </is>
@@ -1529,23 +1529,23 @@
       <c r="Z21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Trade-offs específicos por tipo de aplicação</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Em visão computacional, os dados agrupados formam uma informação sobre a imagem, essa informação precisa ser precisa a imagem, compreensível pela máquina e a depender da quantidade, não pode ser muito grande, ou seja, precisa ser direta e com exatidão. </t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Em visão computacional, os dados agrupados formam uma informação sobre a imagem, essa informação precisa ser precisa a imagem, compreensível pela máquina e a depender da quantidade, não pode ser muito grande, ou seja, precisa ser direta e com exatidão. </t>
         </is>
@@ -1577,24 +1577,24 @@
       <c r="Z22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>Trade-offs e Tensões Inerentes</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Sacrifício da completude pela confiabilidade
 Índice</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>As vezes os dados podem não estarem completos, mas a confiabilidade pode ser mais alta.</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>As vezes os dados podem não estarem completos, mas a confiabilidade pode ser mais alta.</t>
         </is>
@@ -1626,23 +1626,23 @@
       <c r="Z23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Varia segundo o objetivo do aprendizado, fontes e metricas dos rótulos </t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Varia segundo o objetivo do aprendizado, fontes e metricas dos rótulos </t>
         </is>
@@ -1674,23 +1674,23 @@
       <c r="Z24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>Deve-se sempre entender o problema a ser solucionado para dar importância maior para uma característica em detrimento de outras</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>Deve-se sempre entender o problema a ser solucionado para dar importância maior para uma característica em detrimento de outras. A completude, por exemplo, é uma característica muito importante já que os dados precisam estar "completos" para serem alimentados em um sistema de ML. A consistência e a credibilidade, por exemplo, podem ser características a serem balanceadas. Por vezes, encontramos inconsistências em nossas fontes de dados e precisamos optar pela fonte de maior credibilidade</t>
         </is>
@@ -1722,23 +1722,23 @@
       <c r="Z25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>CONSEQUÊNCIAS DA NEGLIGÊNCIA NO EQUILÍBRIO</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Resultado confuso/incompleto e retrabalho</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
         <is>
           <t>O problema é quando os dados nao sao consitentes o incopletos a inferência e resultado final o cliente pode ser confuso e incompleto</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>O problema é quando os dados nao sao consitentes o incopletos a inferência e resultado final o cliente pode ser confuso e incompleto. Precisa de refazer o processo varias vezes isso leva a gastos de infra em todo o fluxo</t>
         </is>
@@ -1770,23 +1770,23 @@
       <c r="Z26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Abordagens iterativas e de validação contínua</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="35" t="inlineStr">
         <is>
           <t>primeiro o resultado e depois avaliar como ele poderia ser melhorado, revisitando essas características</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>O que costumo ver com muita frequência é ver primeiro o resultado e depois avaliar como ele poderia ser melhorado, revisitando essas características. Aqui depende muito do tipo do projeto também.</t>
         </is>
@@ -1818,23 +1818,23 @@
       <c r="Z27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C28" s="4" t="n"/>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="35" t="inlineStr">
         <is>
           <t>Realmente depende do contexto</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>Realmente depende do contexto. Atualmente participo de um projeto que trata anamneses de hospitais. Para manter a conformidade, abordamos soluções de aprendizado de máquina federado, onde os dados permanecem locais.</t>
         </is>
@@ -1866,19 +1866,19 @@
       <c r="Z28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Otimização de formato e infraestrutura computacional</t>
         </is>
       </c>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="35" t="inlineStr">
         <is>
           <t>No geral boas ferramentas de mercado como o databricks ajuda o cientista de dados a focar na solução, pois isso é tratado de forma estratégica e inteligente pelo sistema. Resumindo, escolha bem sua plataforma e defina bem os requisitos do sistema.</t>
         </is>
@@ -1910,23 +1910,23 @@
       <c r="Z29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>AUSÊNCIA DE EXPERIÊNCIA OU CONHECIMENTO</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Não-experiência declarada com desenvolvimento de ML</t>
         </is>
       </c>
       <c r="C30" s="4" t="n"/>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
         <is>
           <t>quando desenvolvo tudo faco por fazer para cada pilar como: disponibilidade, seguranca, confiabilidade e boas praticas</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="35" t="inlineStr">
         <is>
           <t>Nao desenvolvi nenhum sistema com AM mas quando desenvolvo tudo faco por fazer para cada pilar como: disponibilidade, seguranca, confiabilidade e boas praticas</t>
         </is>
@@ -1958,23 +1958,23 @@
       <c r="Z30" s="4" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>VALORAÇÃO GERAL DAS CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Reconhecimento da importância universal</t>
         </is>
       </c>
       <c r="C31" s="4" t="n"/>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="35" t="inlineStr">
         <is>
           <t>São características que definem a qualidade do dado para ser utilizado em soluções de IA</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>São características que definem a qualidade do dado para ser utilizado em soluções de IA</t>
         </is>
@@ -2006,23 +2006,23 @@
       <c r="Z31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>Técnicas de pré-processamento e engenharia de features</t>
         </is>
       </c>
       <c r="C32" s="4" t="n"/>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Após conhecer a amostra começo a tomar decisões sobre como padronizacao, o que deve ser removido ou incrementado, tentando remover os possíveis ruídos para melhorar o resultados finais </t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Eu tento, tudo depende do problema a ser solucionado o conjunto de dados que eu tenha disponível. Após conhecer a amostra começo a tomar decisões sobre como padronizacao, o que deve ser removido ou incrementado, tentando remover os possíveis ruídos para melhorar o resultados finais </t>
         </is>
@@ -2054,23 +2054,23 @@
       <c r="Z32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C33" s="4" t="n"/>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> tudo depende do problema a ser solucionado o conjunto de dados que eu tenha disponível</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Eu tento, tudo depende do problema a ser solucionado o conjunto de dados que eu tenha disponível. Após conhecer a amostra começo a tomar decisões sobre como.pafronizacao, o que deve ser removido ou incrementado, tentando remover os possíveis ruídos para melhorar o.resultados finais </t>
         </is>
@@ -2102,19 +2102,19 @@
       <c r="Z33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Especificidade por domínio crítico</t>
         </is>
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="35" t="inlineStr">
         <is>
           <t>Ser preciso é uma necessidade de negócio em sistemas de Aprendizado de Máquina e isso deve requerer confiabilidade, o que pode impactar na eficiência computacional. Sob esta fala, sistemas de análises médicas permeiam o cenário descrito, afinal imagens clínicas geralmente têm alta resolução pois demandam confiabilidade para apresentação dos laudos. Ou seja, essas imagens representam grandes volumes de dados, impactando na eficiência computacional desse sistema.</t>
         </is>
@@ -2146,23 +2146,23 @@
       <c r="Z34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C35" s="4" t="n"/>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>Dependerá da aplicação, se há requisitos de tempo real ou não, se o tempo de espera para a resposta do modelo é algo sensível ou não, pois isso pode levar a uma maior flexibilidade quanto as taxas de acerto e pririzando a eficiência.</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E35" s="36" t="inlineStr">
         <is>
           <t>Dependerá da aplicação, se há requisitos de tempo real ou não, se o tempo de espera para a resposta do modelo é algo sensível ou não, pois isso pode levar a uma maior flexibilidade quanto as taxas de acerto e pririzando a eficiência.</t>
         </is>
@@ -2194,23 +2194,23 @@
       <c r="Z35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>HIERARQUIZAÇÃO EXPLÍCITA DE CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>Conjunto de características essenciais não-negociáveis</t>
         </is>
       </c>
       <c r="C36" s="4" t="n"/>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Precisão, Completude, Consistência, Credibilidade eu considero essenciais não importa a situação, pois sem esses pontos todos os passos seguintes num fluxo de ciência de dados se tornam irrelevante, pois o resultado deixa de ser confiável</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="35" t="inlineStr">
         <is>
           <t>Algumas características, como Precisão, Completude, Consistência, Credibilidade eu considero essenciais não importa a situação, pois sem esses pontos todos os passos seguintes num fluxo de ciência de dados se tornam irrelevante, pois o resultado deixa de ser confiável (ou seja afeta negativamente a Confiabilidade). Na minha opinião, se o produto final não é confiável ele não deveria estar em produção. Apenas para fins de pesquisa de existe um valor em dados e modelos menos confiáveis (mas todo o trabalho deve ser feito sabendo desse problema.)   Caso esses problemas não sejam identificados e passem por exemplo até o passo de treinamento de um modelo, onde se descobre que o modelo não é confiável, torna-se importante outros fatores como Rastreabilidade e Recuperabilidade para permitir que sejam identificados os problemas e caso necessário que seja gerado um conjunto corrigido de dados caso possível.  Com relação a outras características dos dados, tudo depende de qual será a aplicação. Atualidade, especificamente, é um grande exemplo de uma característica que pode ser extremamente prioritária para certas aplicações (como por exemplo meteorologia, serviços críticos, bancários, etc.) mas que também pode ser desnecessário dependendo do objetivo.   Com relação as outras características não mencionadas, como compreensibilidade e disponibilidade, creio que para fins de pesquisa são importantes, mas pensando num fluxo de construção de produto que iria para a produção, a ideia é que tendo uma aplicação já pronta, esses fatores seriam menos importantes até que fosse necessária uma atualização do produto. No geral, eu acredito que essas características são mais importantes para o produto final do que para os dados.</t>
         </is>
@@ -2242,23 +2242,23 @@
       <c r="Z36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Trade-offs específicos por tipo de aplicação</t>
         </is>
       </c>
       <c r="C37" s="4" t="n"/>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">"Em sistemas biométricos que trabalhei, a eficiência era um ponto bem critico, pois não poderíamos aceitar falsos positivos",  "tínhamos etapas de limpezas bem complexas priorizando a questão da eficiência e precisão posterior dos algoritmos de identificação a serem treinados", </t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="35" t="inlineStr">
         <is>
           <t>Em sistemas biométricos que trabalhei, a eficiência era um ponto bem critico, pois não poderíamos aceitar falsos positivos. Nesses casos tínhamos etapas de limpezas bem complexas priorizando a questão da eficiência e precisão posterior dos algoritmos de identificação a serem treinados. Em outros casos como classificação de texto, houveram sim preocupações com compreensibilidade, e menos com eficiência, sendo que nesses esse casos trabalhávamos com rankeamento, e a classificação tinha uma etapa de validação humana após a execução do modelo treinado.</t>
         </is>
@@ -2290,23 +2290,23 @@
       <c r="Z37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>Técnicas de pré-processamento e engenharia de features</t>
         </is>
       </c>
       <c r="C38" s="4" t="n"/>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="35" t="inlineStr">
         <is>
           <t>Através dos treinamentos com diferentes configurações e diferentes tipos de dados. Através desse tuning inicial é possível inclusive excluir dados que não venham a acrescentar muito no resultado final do modelo pretendido</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="35" t="inlineStr">
         <is>
           <t>Através dos treinamentos com diferentes configurações e diferentes tipos de dados. Através desse tuning inicial é possível inclusive excluir dados que não venham a acrescentar muito no resultado final do modelo pretendido. Uma Feature Selection pode ser utilizada nesse sentido.</t>
         </is>
@@ -2338,23 +2338,23 @@
       <c r="Z38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="35" t="inlineStr">
         <is>
           <t>Especificidade por domínio crítico</t>
         </is>
       </c>
       <c r="C39" s="4" t="n"/>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="35" t="inlineStr">
         <is>
           <t>situações que lidam com saúde, vida e morte, por exemplo, deve considerar apenas dados de boa qualidade com relação a todas as características. Qualquer dado não confiável deve ser eliminado. Em outros casos, talvez possamos ser menos rigorosos com relação a alguma caracaterística.</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="35" t="inlineStr">
         <is>
           <t>Dependendo do problema/domínio sendo estudado, esse equilíbrio pode variar. Por exemplo, situações que lidam com saúde, vida e morte, por exemplo, deve considerar apenas dados de boa qualidade com relação a todas as características. Qualquer dado não confiável deve ser eliminado. Em outros casos, talvez possamos ser menos rigorosos com relação a alguma caracaterística.</t>
         </is>
@@ -2386,23 +2386,23 @@
       <c r="Z39" s="4" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="35" t="inlineStr">
         <is>
           <t>Especificidade por domínio crítico</t>
         </is>
       </c>
       <c r="C40" s="4" t="n"/>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Projetos que envolvem saúde ou dinheiro são mais críticos em relação à alguns pontos. Agora alguns tipos de classificação podem ter outras prioridades.</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="35" t="inlineStr">
         <is>
           <t>Depende muito do projeto. Projetos que envolvem saúde ou dinheiro são mais críticos em relação à alguns pontos. Agora alguns tipos de classificação podem ter outras prioridades.</t>
         </is>
@@ -2434,23 +2434,23 @@
       <c r="Z40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>HIERARQUIZAÇÃO EXPLÍCITA DE CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>Conjunto de características essenciais não-negociáveis</t>
         </is>
       </c>
       <c r="C41" s="4" t="n"/>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
         <is>
           <t>infelizmente talvez não tenhamos opções nem de equilibrar. Mas completude, precisão, e credibilidade devem ser prioritários.</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="35" t="inlineStr">
         <is>
           <t>Dependendo da situação, infelizmente talvez não tenhamos opções nem de equilibrar. Mas completude, precisão, e credibilidade devem ser prioritários.</t>
         </is>
@@ -2482,23 +2482,23 @@
       <c r="Z41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>RESTRIÇÕES ORGANIZACIONAIS E PRÁTICAS</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="35" t="inlineStr">
         <is>
           <t>Restrições de equipe, prazos e cultura organizacional</t>
         </is>
       </c>
       <c r="C42" s="4" t="n"/>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">"Faço muito uso de dados desequências de DNA, tais caracteristicas estão relacionadas com a plataforma que se utiliza, sendo assim tento manter sempre plataformas atualizadas", "conciliar as caracteristicas tem.uma relacao maior com o trabalho da equipe do projeto e os prazos de entrega.", </t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E42" s="35" t="inlineStr">
         <is>
           <t>Depende da criticisade do modelo, onde ele vai ser implementado e as politicas da equipe de trabalho. Muitas vezes conciliar as caracteristicas tem.uma relacao maior com o trabalho da equipe do projeto e os prazos de entrega. Ainda temos dificuldade de que  vonsiderem o estudo previo dos dados como entregavel de uma sprint pois acham que modelos sao como pasteis, feitos rapidos, com qualquer dados e tecnologia. E  resolve o mundo</t>
         </is>
@@ -2530,23 +2530,23 @@
       <c r="Z42" s="4" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>RESTRIÇÕES ORGANIZACIONAIS E PRÁTICAS</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="35" t="inlineStr">
         <is>
           <t>Dependência de plataformas e ferramentas externas</t>
         </is>
       </c>
       <c r="C43" s="4" t="n"/>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Faço muito uso de dados desequências de DNA, tais caracteristicas estão relacionadas com a plataforma que se utiliza, sendo assim tento manter sempre plataformas atualizadas </t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Faço muito uso de dados desequências de DNA, tais caracteristicas estão relacionadas com a plataforma que se utiliza, sendo assim tento manter sempre plataformas atualizadas </t>
         </is>
@@ -2578,23 +2578,23 @@
       <c r="Z43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="35" t="inlineStr">
         <is>
           <t>Abordagens iterativas e de validação contínua</t>
         </is>
       </c>
       <c r="C44" s="4" t="n"/>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="35" t="inlineStr">
         <is>
           <t>É procurar entregar um MVP com os dados que temos. Em seguida, deixar nas mãos do negócio para decisões de onde o projeto irá.</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E44" s="36" t="inlineStr">
         <is>
           <t>É procurar entregar um MVP com os dados que temos. Em seguida, deixar nas mãos do negócio para decisões de onde o projeto irá.</t>
         </is>
@@ -2626,23 +2626,23 @@
       <c r="Z44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>CONSEQUÊNCIAS DA NEGLIGÊNCIA NO EQUILÍBRIO</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>Critério humano como termômetro da qualidade</t>
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="35" t="inlineStr">
         <is>
           <t>If a human could not do proper desicions on data due to its flaws, then one should be careful.</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="36" t="inlineStr">
         <is>
           <t>If a human could not do proper desicions on data due to its flaws, then one should be careful.</t>
         </is>
@@ -2674,23 +2674,23 @@
       <c r="Z45" s="4" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>VALORAÇÃO GERAL DAS CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="35" t="inlineStr">
         <is>
           <t>Reconhecimento da importância universal</t>
         </is>
       </c>
       <c r="C46" s="4" t="n"/>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="35" t="inlineStr">
         <is>
           <t>They are very important and we must consider all of them</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="36" t="inlineStr">
         <is>
           <t>They are very important and we must consider all of them</t>
         </is>
@@ -2722,23 +2722,23 @@
       <c r="Z46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="35" t="inlineStr">
         <is>
           <t>Técnicas de pré-processamento e engenharia de features</t>
         </is>
       </c>
       <c r="C47" s="4" t="n"/>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="35" t="inlineStr">
         <is>
           <t>“Detención de anomalías y valores atípicos o datos incompletos, se toma la decisión de corregir estos errores, eliminar los outliers.”, “Preparación y procesamiento de datos, realizando transformaciones o codificación de datos para garantizar la completitud y la consistencia.”</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E47" s="35" t="inlineStr">
         <is>
           <t>Detención de anomalías y valores atípicos o datos incompletos, se toma la decisión de corregir estos errores, eliminar los outliers.
 Preparación y procesamiento de datos, realizando transformaciones o codificación de datos para garantizar la completitud y la consistencia</t>
@@ -2771,23 +2771,23 @@
       <c r="Z47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>AUSÊNCIA DE EXPERIÊNCIA OU CONHECIMENTO</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="35" t="inlineStr">
         <is>
           <t>Não-experiência declarada com desenvolvimento de ML</t>
         </is>
       </c>
       <c r="C48" s="4" t="n"/>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>I have never handled with this issue</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E48" s="36" t="inlineStr">
         <is>
           <t>I have never handled with this issue</t>
         </is>
@@ -2819,23 +2819,23 @@
       <c r="Z48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>HIERARQUIZAÇÃO EXPLÍCITA DE CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="35" t="inlineStr">
         <is>
           <t>Precisão como prioridade máxima</t>
         </is>
       </c>
       <c r="C49" s="4" t="n"/>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D49" s="35" t="inlineStr">
         <is>
           <t>“Based on the scale of the project, mostly focused on accuracy and utilising cloud solutions for computational efficiency.”</t>
         </is>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E49" s="35" t="inlineStr">
         <is>
           <t>Based on the scale of the project, mostly focused on accuracy and utilising cloud solutions for computational efficiency. Made peace with the fact that black box algorithms exist and not everything could be explained</t>
         </is>
@@ -2867,23 +2867,23 @@
       <c r="Z49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C50" s="4" t="n"/>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="35" t="inlineStr">
         <is>
           <t>"It depends, each case is different"</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E50" s="36" t="inlineStr">
         <is>
           <t>It depends, each case is different</t>
         </is>
@@ -2915,24 +2915,24 @@
       <c r="Z50" s="4" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Não-engajamento com a questão dos atributos
 </t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B51" s="35" t="inlineStr">
         <is>
           <t>AUSÊNCIA DE EXPERIÊNCIA OU CONHECIMENTO</t>
         </is>
       </c>
       <c r="C51" s="4" t="n"/>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">We simply work on the data we have available. </t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E51" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">To be honest I dont look at computacional efficiency and Im not sure if the data scientists of my team do this. Typically, we dont negotiate these attributes. We simply work on the data we have available. </t>
         </is>
@@ -2964,23 +2964,23 @@
       <c r="Z51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>AUSÊNCIA DE EXPERIÊNCIA OU CONHECIMENTO</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="35" t="inlineStr">
         <is>
           <t>Não-engajamento com a questão dos atributos</t>
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="35" t="inlineStr">
         <is>
           <t>“To be honest I dont look at computacional efficiency and Im not sure if the data scientists of my team do this.”,“We simply work on the data we have available.”</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E52" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">To be honest I dont look at computacional efficiency and Im not sure if the data scientists of my team do this. Typically, we dont negotiate these attributes. We simply work on the data we have available. </t>
         </is>
@@ -3012,23 +3012,23 @@
       <c r="Z52" s="4" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="35" t="inlineStr">
         <is>
           <t>Especificidade por domínio crítico</t>
         </is>
       </c>
       <c r="C53" s="4" t="n"/>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> It's a trade-off. Accuracy vs. speed, mostly. For medical, accuracy wins. For real-time, speed</t>
         </is>
       </c>
-      <c r="E53" s="16" t="inlineStr">
+      <c r="E53" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> It's a trade-off. Accuracy vs. speed, mostly. For medical, accuracy wins. For real-time, speed. We try to keep things understandable, but project goals dictate the balance.</t>
         </is>
@@ -3060,23 +3060,23 @@
       <c r="Z53" s="4" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B54" s="35" t="inlineStr">
         <is>
           <t>Abordagens iterativas e de validação contínua</t>
         </is>
       </c>
       <c r="C54" s="4" t="n"/>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="35" t="inlineStr">
         <is>
           <t>“In the early stages of development, the most important factor is achieving high accuracy, even if the code is not optimized or easy to understand.”, “Some optimizations can be performed early on to speed up computations, but only if they don't consume a large portion of the available development time.”, “In the final stages of development, meetings can be scheduled to discuss comprehensibility and determine how improvements will be implemented.”</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr">
+      <c r="E54" s="36" t="inlineStr">
         <is>
           <t>In the early stages of development, the most important factor is achieving high accuracy, even if the code is not optimized or easy to understand. Some optimizations can be performed early on to speed up computations, but only if they don't consume a large portion of the available development time. In the final stages of development, meetings can be scheduled to discuss comprehensibility and determine how improvements will be implemented</t>
         </is>
@@ -3108,23 +3108,23 @@
       <c r="Z54" s="4" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>AUSÊNCIA DE EXPERIÊNCIA OU CONHECIMENTO</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B55" s="35" t="inlineStr">
         <is>
           <t>Não-experiência declarada com desenvolvimento de ML</t>
         </is>
       </c>
       <c r="C55" s="4" t="n"/>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="35" t="inlineStr">
         <is>
           <t>I don't know, really not familiar with this area.</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr">
+      <c r="E55" s="36" t="inlineStr">
         <is>
           <t>I don't know, really not familiar with this area.</t>
         </is>
@@ -3156,23 +3156,23 @@
       <c r="Z55" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>HIERARQUIZAÇÃO EXPLÍCITA DE CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B56" s="35" t="inlineStr">
         <is>
           <t>Priorização da disponibilidade/dados como pré-requisito</t>
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D56" s="35" t="inlineStr">
         <is>
           <t>the availibility and similar of data was more important than the efficiency, thats then a later prolem and task for implementing efficient dataloaders, but without the date next steps are obsolete</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
+      <c r="E56" s="36" t="inlineStr">
         <is>
           <t>the availibility and similar of data was more important than the efficiency, thats then a later prolem and task for implementing efficient dataloaders, but without the date next steps are obsolete</t>
         </is>
@@ -3204,23 +3204,23 @@
       <c r="Z56" s="4" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>AUSÊNCIA DE EXPERIÊNCIA OU CONHECIMENTO</t>
         </is>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B57" s="35" t="inlineStr">
         <is>
           <t>Não-engajamento com a questão dos atributos</t>
         </is>
       </c>
       <c r="C57" s="4" t="n"/>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
         <is>
           <t>"What everyone cares is the training result, as a mature engineer it should be essential to make system work then consider other priorities "</t>
         </is>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">What everyone cares is the training result, as a mature engineer it should be essential to make system work then consider other priorities </t>
         </is>
@@ -3252,23 +3252,23 @@
       <c r="Z57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+      <c r="A58" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="35" t="inlineStr">
         <is>
           <t>Trade-offs específicos por tipo de aplicação</t>
         </is>
       </c>
       <c r="C58" s="4" t="n"/>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">in a task like text classification where introducing false positives haves little harm, precision in the data becomes less critical, and I will instead prioritize completeness, accessibility, and traceability. </t>
         </is>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E58" s="35" t="inlineStr">
         <is>
           <t>For me, balancing data quality characteristics fundamentally depends on the required metrics of the ML model being built and the domain of the data. If precision is the utmost priority,  for instance in a high-stakes classification task , I would favor data accuracy, credibility, and timeliness over attributes like computational efficiency. On the other hand, in a task like text classification where introducing false positives haves little harm, precision in the data becomes less critical, and I will instead prioritize completeness, accessibility, and traceability. An example from my research is my work on design discussion detection using transformer models, where the scarcity of labeled data and high annotation costs meant I had to prioritize data completeness and accessibility — accepting a reduced but well-curated dataset — over having a perfectly precise, fully annotated corpus. So basically, the ML model's target metrics and the risk profile of its errors should always drive which data quality characteristics you optimize for.</t>
         </is>
@@ -3300,23 +3300,23 @@
       <c r="Z58" s="4" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B59" s="35" t="inlineStr">
         <is>
           <t>Especificidade por domínio crítico</t>
         </is>
       </c>
       <c r="C59" s="4" t="n"/>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D59" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> If precision is the utmost priority,  for instance in a high-stakes classification task , I would favor data accuracy, credibility, and timeliness over attributes like computational efficiency</t>
         </is>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E59" s="35" t="inlineStr">
         <is>
           <t>For me, balancing data quality characteristics fundamentally depends on the required metrics of the ML model being built and the domain of the data. If precision is the utmost priority,  for instance in a high-stakes classification task , I would favor data accuracy, credibility, and timeliness over attributes like computational efficiency. On the other hand, in a task like text classification where introducing false positives haves little harm, precision in the data becomes less critical, and I will instead prioritize completeness, accessibility, and traceability. An example from my research is my work on design discussion detection using transformer models, where the scarcity of labeled data and high annotation costs meant I had to prioritize data completeness and accessibility — accepting a reduced but well-curated dataset — over having a perfectly precise, fully annotated corpus. So basically, the ML model's target metrics and the risk profile of its errors should always drive which data quality characteristics you optimize for.</t>
         </is>
@@ -3348,23 +3348,23 @@
       <c r="Z59" s="4" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr">
+      <c r="B60" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C60" s="4" t="n"/>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D60" s="35" t="inlineStr">
         <is>
           <t>balancing data quality characteristics fundamentally depends on the required metrics of the ML model being built and the domain of the data.</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E60" s="35" t="inlineStr">
         <is>
           <t>For me, balancing data quality characteristics fundamentally depends on the required metrics of the ML model being built and the domain of the data. If precision is the utmost priority,  for instance in a high-stakes classification task , I would favor data accuracy, credibility, and timeliness over attributes like computational efficiency. On the other hand, in a task like text classification where introducing false positives haves little harm, precision in the data becomes less critical, and I will instead prioritize completeness, accessibility, and traceability. An example from my research is my work on design discussion detection using transformer models, where the scarcity of labeled data and high annotation costs meant I had to prioritize data completeness and accessibility — accepting a reduced but well-curated dataset — over having a perfectly precise, fully annotated corpus. So basically, the ML model's target metrics and the risk profile of its errors should always drive which data quality characteristics you optimize for.</t>
         </is>
@@ -3396,23 +3396,23 @@
       <c r="Z60" s="4" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>Trade-offs e Tensões Inerentes</t>
         </is>
       </c>
-      <c r="B61" s="16" t="inlineStr">
+      <c r="B61" s="35" t="inlineStr">
         <is>
           <t>Sacrifício da precisão/anotação por restrições de custo e disponibilidade de rótulos</t>
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D61" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> "on design discussion detection using transformer models, where the scarcity of labeled data and high annotation costs meant I had to prioritize data completeness and accessibility — accepting a reduced but well-curated dataset — ML model's target metrics and the risk profile of its errors should always drive which data quality characteristics you optimize for.”</t>
         </is>
       </c>
-      <c r="E61" s="16" t="inlineStr">
+      <c r="E61" s="35" t="inlineStr">
         <is>
           <t>For me, balancing data quality characteristics fundamentally depends on the required metrics of the ML model being built and the domain of the data. 
 If precision is the utmost priority,  for instance in a high-stakes classification task , I would favor data accuracy, credibility, and timeliness over attributes like computational efficiency. 
@@ -3447,23 +3447,23 @@
       <c r="Z61" s="4" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B62" s="35" t="inlineStr">
         <is>
           <t>Dependência genérica do contexto/projeto/problema</t>
         </is>
       </c>
       <c r="C62" s="4" t="n"/>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="D62" s="35" t="inlineStr">
         <is>
           <t>"It really depends on the business requirements and the problem that we are solving"</t>
         </is>
       </c>
-      <c r="E62" s="17" t="inlineStr">
+      <c r="E62" s="36" t="inlineStr">
         <is>
           <t>It really depends on the business requirements and the problem that we are solving</t>
         </is>
@@ -3495,23 +3495,23 @@
       <c r="Z62" s="4" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr">
+      <c r="A63" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="B63" s="35" t="inlineStr">
         <is>
           <t>Especificidade por domínio crítico</t>
         </is>
       </c>
       <c r="C63" s="4" t="n"/>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="D63" s="35" t="inlineStr">
         <is>
           <t>"In Finance, the focus was often on speed and precision.",  “In Healthcare, the focus is more on explainability and safety.”</t>
         </is>
       </c>
-      <c r="E63" s="17" t="inlineStr">
+      <c r="E63" s="36" t="inlineStr">
         <is>
           <t>In Finance, the focus was often on speed and precision. In Healthcare, the focus is more on explainability and safety.</t>
         </is>
@@ -3543,24 +3543,24 @@
       <c r="Z63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="A64" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Trade-offs e Tensões Inerentes
 </t>
         </is>
       </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B64" s="35" t="inlineStr">
         <is>
           <t>Trade-off como condição estrutura</t>
         </is>
       </c>
       <c r="C64" s="4" t="n"/>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D64" s="35" t="inlineStr">
         <is>
           <t>I balance them according to the desired goals and the systems constraints.</t>
         </is>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E64" s="35" t="inlineStr">
         <is>
           <t>I balance them according to the desired goals and the systems constraints. For example, in IoT or real-time systems, I would prioritize efficiency. In contrast, in critical systems, I would prioritize accuracy and reliability. The decision depends on how the model will be used in practice.</t>
         </is>
@@ -3592,23 +3592,23 @@
       <c r="Z64" s="4" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="A65" s="35" t="inlineStr">
         <is>
           <t>PRIORIZAÇÃO CONTEXTUAL E DEPENDÊNCIA DE DOMÍNIO</t>
         </is>
       </c>
-      <c r="B65" s="16" t="inlineStr">
+      <c r="B65" s="35" t="inlineStr">
         <is>
           <t>Especificidade por domínio crítico</t>
         </is>
       </c>
       <c r="C65" s="4" t="n"/>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D65" s="35" t="inlineStr">
         <is>
           <t>“I balance them according to the desired goals and the systems constraints.”, "in IoT or real-time systems, I would prioritize efficiency.”, "in critical systems, I would prioritize accuracy and reliability.”, “The decision depends on how the model will be used in practice.”</t>
         </is>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E65" s="35" t="inlineStr">
         <is>
           <t>I balance them according to the desired goals and the systems constraints. For example, in IoT or real-time systems, I would prioritize efficiency. In contrast, in critical systems, I would prioritize accuracy and reliability. The decision depends on how the model will be used in practice.</t>
         </is>
@@ -3640,23 +3640,23 @@
       <c r="Z65" s="4" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="A66" s="35" t="inlineStr">
         <is>
           <t>VALORAÇÃO GERAL DAS CARACTERÍSTICAS</t>
         </is>
       </c>
-      <c r="B66" s="16" t="inlineStr">
+      <c r="B66" s="35" t="inlineStr">
         <is>
           <t>Reconhecimento da importância universal</t>
         </is>
       </c>
       <c r="C66" s="4" t="n"/>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="35" t="inlineStr">
         <is>
           <t>Em específico para essas características definidas no enunciado, é fácil equilibrá-las, já que não existe competitividade entre elas. Contudo, entendo que, uma vez que a precisão dos dados tenha sido alcançada e que a compreensão a respeito deles tenha sido garantida</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E66" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Em específico para essas características definidas no enunciado, é fácil equilibrá-las, já que não existe competitividade entre elas. Contudo, entendo que, uma vez que a precisão dos dados tenha sido alcançada e que a compreensão a respeito deles tenha sido garantida (seja pela clareza da documentação, compreensão da equipe de desenvolvimento ou pela presença de um "especialista de domínio"), o ponto crítico é a eficiência, que deve ser garantida tanto pelo tratamento dos dados quanto pela infraestrutura utilizada para o processamento: 1) é preciso que os dados sejam otimizados para o processamento (recentemente, consegui tonar um projeto exequível passando os dados do formato separado por vírgulas -- csv -- para o formato apache parquet, geralmente utilizado em projetos de Big Data e, assim, o tornei mais eficiente, passando-o de 8gb para 800mb); 2) contudo, para tudo há um limite e, por vezes, é necessário decidir se não seria estratégico realizar um upgrade vertical ou horizontal da infraestrutura física utilizada, opções essas dentre as quais o último caso (scale-out) costuma apresentar resultados melhores, por se tratar de um processamento distribuído. </t>
         </is>
@@ -3688,23 +3688,23 @@
       <c r="Z66" s="4" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="A67" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B67" s="16" t="inlineStr">
+      <c r="B67" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Otimização de formato e infraestrutura computacional</t>
         </is>
       </c>
       <c r="C67" s="4" t="n"/>
-      <c r="D67" s="16" t="inlineStr">
+      <c r="D67" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> o ponto crítico é a eficiência, que deve ser garantida tanto pelo tratamento dos dados quanto pela infraestrutura utilizada para o processamento: 1) é preciso que os dados sejam otimizados para o processamento</t>
         </is>
       </c>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E67" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Em específico para essas características definidas no enunciado, é fácil equilibrá-las, já que não existe competitividade entre elas. Contudo, entendo que, uma vez que a precisão dos dados tenha sido alcançada e que a compreensão a respeito deles tenha sido garantida (seja pela clareza da documentação, compreensão da equipe de desenvolvimento ou pela presença de um "especialista de domínio"), o ponto crítico é a eficiência, que deve ser garantida tanto pelo tratamento dos dados quanto pela infraestrutura utilizada para o processamento: 1) é preciso que os dados sejam otimizados para o processamento (recentemente, consegui tonar um projeto exequível passando os dados do formato separado por vírgulas -- csv -- para o formato apache parquet, geralmente utilizado em projetos de Big Data e, assim, o tornei mais eficiente, passando-o de 8gb para 800mb); 2) contudo, para tudo há um limite e, por vezes, é necessário decidir se não seria estratégico realizar um upgrade vertical ou horizontal da infraestrutura física utilizada, opções essas dentre as quais o último caso (scale-out) costuma apresentar resultados melhores, por se tratar de um processamento distribuído. </t>
         </is>
@@ -3736,23 +3736,23 @@
       <c r="Z67" s="4" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="inlineStr">
+      <c r="A68" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B68" s="16" t="inlineStr">
+      <c r="B68" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Otimização de formato e infraestrutura computacional</t>
         </is>
       </c>
       <c r="C68" s="4" t="n"/>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="35" t="inlineStr">
         <is>
           <t>por vezes, é necessário decidir se não seria estratégico realizar um upgrade vertical ou horizontal da infraestrutura física utilizada</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E68" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Em específico para essas características definidas no enunciado, é fácil equilibrá-las, já que não existe competitividade entre elas. Contudo, entendo que, uma vez que a precisão dos dados tenha sido alcançada e que a compreensão a respeito deles tenha sido garantida (seja pela clareza da documentação, compreensão da equipe de desenvolvimento ou pela presença de um "especialista de domínio"), o ponto crítico é a eficiência, que deve ser garantida tanto pelo tratamento dos dados quanto pela infraestrutura utilizada para o processamento: 1) é preciso que os dados sejam otimizados para o processamento (recentemente, consegui tonar um projeto exequível passando os dados do formato separado por vírgulas -- csv -- para o formato apache parquet, geralmente utilizado em projetos de Big Data e, assim, o tornei mais eficiente, passando-o de 8gb para 800mb); 2) contudo, para tudo há um limite e, por vezes, é necessário decidir se não seria estratégico realizar um upgrade vertical ou horizontal da infraestrutura física utilizada, opções essas dentre as quais o último caso (scale-out) costuma apresentar resultados melhores, por se tratar de um processamento distribuído. </t>
         </is>
@@ -3784,23 +3784,23 @@
       <c r="Z68" s="4" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="A69" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B69" s="16" t="inlineStr">
+      <c r="B69" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Otimização de formato e infraestrutura computacional</t>
         </is>
       </c>
       <c r="C69" s="4" t="n"/>
-      <c r="D69" s="16" t="inlineStr">
+      <c r="D69" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">“O último caso (scale-out) costuma apresentar resultados melhores, por se tratar de um processamento distribuído.” </t>
         </is>
       </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="E69" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Em específico para essas características definidas no enunciado, é fácil equilibrá-las, já que não existe competitividade entre elas. Contudo, entendo que, uma vez que a precisão dos dados tenha sido alcançada e que a compreensão a respeito deles tenha sido garantida (seja pela clareza da documentação, compreensão da equipe de desenvolvimento ou pela presença de um "especialista de domínio"), o ponto crítico é a eficiência, que deve ser garantida tanto pelo tratamento dos dados quanto pela infraestrutura utilizada para o processamento: 1) é preciso que os dados sejam otimizados para o processamento (recentemente, consegui tonar um projeto exequível passando os dados do formato separado por vírgulas -- csv -- para o formato apache parquet, geralmente utilizado em projetos de Big Data e, assim, o tornei mais eficiente, passando-o de 8gb para 800mb); 2) contudo, para tudo há um limite e, por vezes, é necessário decidir se não seria estratégico realizar um upgrade vertical ou horizontal da infraestrutura física utilizada, opções essas dentre as quais o último caso (scale-out) costuma apresentar resultados melhores, por se tratar de um processamento distribuído. </t>
         </is>
@@ -3832,23 +3832,23 @@
       <c r="Z69" s="4" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="inlineStr">
+      <c r="A70" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> Escolha do modelo conforme prioridade</t>
         </is>
       </c>
       <c r="C70" s="4" t="n"/>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D70" s="35" t="inlineStr">
         <is>
           <t>I chose a logistic regression model, a decision that prioritized an interpretable and reproducible architecture over more complex models</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E70" s="35" t="inlineStr">
         <is>
           <t>In one of my latest machine learning projects using an adult income dataset, I chose a logistic regression model, a decision that prioritized an interpretable and reproducible architecture over more complex models. Furthermore, to reconcile computational efficiency with predictive power, I created a new atribute (capital-net) by consolidanting both capital gain and loss, simplifying the input matrix while retaining essential data.</t>
         </is>
@@ -3880,23 +3880,23 @@
       <c r="Z70" s="4" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="inlineStr">
+      <c r="A71" s="35" t="inlineStr">
         <is>
           <t>ESTRATÉGIAS DE EQUILÍBRIO E TÉCNICAS DE CONCILIAÇÃO</t>
         </is>
       </c>
-      <c r="B71" s="16" t="inlineStr">
+      <c r="B71" s="35" t="inlineStr">
         <is>
           <t>Técnicas de pré-processamento e engenharia de features</t>
         </is>
       </c>
       <c r="C71" s="4" t="n"/>
-      <c r="D71" s="16" t="inlineStr">
+      <c r="D71" s="35" t="inlineStr">
         <is>
           <t>“I created a new attribute (capital-net) by consolidating both capital gain and loss”</t>
         </is>
       </c>
-      <c r="E71" s="16" t="inlineStr">
+      <c r="E71" s="35" t="inlineStr">
         <is>
           <t>In one of my latest machine learning projects using an adult income dataset, I chose a logistic regression model, a decision that prioritized an interpretable and reproducible architecture over more complex models. Furthermore, to reconcile computational efficiency with predictive power, I created a new atribute (capital-net) by consolidanting both capital gain and loss, simplifying the input matrix while retaining essential data.</t>
         </is>
@@ -3928,23 +3928,23 @@
       <c r="Z71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="inlineStr">
+      <c r="A72" s="35" t="inlineStr">
         <is>
           <t>TRADE-OFFS E TENSÕES INERENTES</t>
         </is>
       </c>
-      <c r="B72" s="16" t="inlineStr">
+      <c r="B72" s="35" t="inlineStr">
         <is>
           <t>Trade-off explícito como condição estrutural do trabalho em ML</t>
         </is>
       </c>
       <c r="C72" s="4" t="n"/>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D72" s="35" t="inlineStr">
         <is>
           <t>Balancing data quality in real-world machine learning projects is essentially a constant game of trade-offs, as you can rarely optimize for everything at once</t>
         </is>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="E72" s="35" t="inlineStr">
         <is>
           <t>Balancing data quality in real-world machine learning projects is essentially a constant game of trade-offs, as you can rarely optimize for everything at once. For instance, highly accurate models demand massive amounts of computing power, so you often have to settle for a slightly less precise but much faster model just to make it practical to run in production. Similarly, while neatly organized and highly structured databases are great for developers to read and understand, they are notoriously slow for training, meaning we usually end up flattening the data into ugly, denormalized tables so the algorithms can ingest them efficiently. Even when building the dataset itself, trying to keep every single messy record just to maximize completeness usually introduces too much noise, making it far better to simply throw out the bad data and accept a smaller dataset in exchange for a much more accurate and reliable model.</t>
         </is>
@@ -3976,23 +3976,23 @@
       <c r="Z72" s="4" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="inlineStr">
+      <c r="A73" s="35" t="inlineStr">
         <is>
           <t>TRADE-OFFS E TENSÕES INERENTES</t>
         </is>
       </c>
-      <c r="B73" s="16" t="inlineStr">
+      <c r="B73" s="35" t="inlineStr">
         <is>
           <t>Sacrifício da precisão pela viabilidade computacional</t>
         </is>
       </c>
       <c r="C73" s="4" t="n"/>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D73" s="35" t="inlineStr">
         <is>
           <t>highly accurate models demand massive amounts of computing power, so you often have to settle for a slightly less precise but much faster model just to make it practical to run in production</t>
         </is>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E73" s="35" t="inlineStr">
         <is>
           <t>Balancing data quality in real-world machine learning projects is essentially a constant game of trade-offs, as you can rarely optimize for everything at once. For instance, highly accurate models demand massive amounts of computing power, so you often have to settle for a slightly less precise but much faster model just to make it practical to run in production. Similarly, while neatly organized and highly structured databases are great for developers to read and understand, they are notoriously slow for training, meaning we usually end up flattening the data into ugly, denormalized tables so the algorithms can ingest them efficiently. Even when building the dataset itself, trying to keep every single messy record just to maximize completeness usually introduces too much noise, making it far better to simply throw out the bad data and accept a smaller dataset in exchange for a much more accurate and reliable model.</t>
         </is>
@@ -4024,23 +4024,23 @@
       <c r="Z73" s="4" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+      <c r="A74" s="35" t="inlineStr">
         <is>
           <t>TRADE-OFFS E TENSÕES INERENTES</t>
         </is>
       </c>
-      <c r="B74" s="16" t="inlineStr">
+      <c r="B74" s="35" t="inlineStr">
         <is>
           <t>Sacrifício da estrutura/legibilidade pela eficiência de treinamento</t>
         </is>
       </c>
       <c r="C74" s="4" t="n"/>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="35" t="inlineStr">
         <is>
           <t>neatly organized and highly structured databases are great for developers to read and understand, they are notoriously slow for training</t>
         </is>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E74" s="35" t="inlineStr">
         <is>
           <t>Balancing data quality in real-world machine learning projects is essentially a constant game of trade-offs, as you can rarely optimize for everything at once. For instance, highly accurate models demand massive amounts of computing power, so you often have to settle for a slightly less precise but much faster model just to make it practical to run in production. Similarly, while neatly organized and highly structured databases are great for developers to read and understand, they are notoriously slow for training, meaning we usually end up flattening the data into ugly, denormalized tables so the algorithms can ingest them efficiently. Even when building the dataset itself, trying to keep every single messy record just to maximize completeness usually introduces too much noise, making it far better to simply throw out the bad data and accept a smaller dataset in exchange for a much more accurate and reliable model.</t>
         </is>
@@ -4072,23 +4072,23 @@
       <c r="Z74" s="4" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="inlineStr">
+      <c r="A75" s="35" t="inlineStr">
         <is>
           <t>TRADE-OFFS E TENSÕES INERENTES</t>
         </is>
       </c>
-      <c r="B75" s="16" t="inlineStr">
+      <c r="B75" s="35" t="inlineStr">
         <is>
           <t>Sacrifício da estrutura/legibilidade pela eficiência de treinamento</t>
         </is>
       </c>
       <c r="C75" s="4" t="n"/>
-      <c r="D75" s="16" t="inlineStr">
+      <c r="D75" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve"> we usually end up flattening the data into ugly, denormalized tables so the algorithms can ingest them efficiently.</t>
         </is>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="35" t="inlineStr">
         <is>
           <t>Balancing data quality in real-world machine learning projects is essentially a constant game of trade-offs, as you can rarely optimize for everything at once. For instance, highly accurate models demand massive amounts of computing power, so you often have to settle for a slightly less precise but much faster model just to make it practical to run in production. Similarly, while neatly organized and highly structured databases are great for developers to read and understand, they are notoriously slow for training, meaning we usually end up flattening the data into ugly, denormalized tables so the algorithms can ingest them efficiently. Even when building the dataset itself, trying to keep every single messy record just to maximize completeness usually introduces too much noise, making it far better to simply throw out the bad data and accept a smaller dataset in exchange for a much more accurate and reliable model.</t>
         </is>
@@ -4120,23 +4120,23 @@
       <c r="Z75" s="4" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="inlineStr">
+      <c r="A76" s="35" t="inlineStr">
         <is>
           <t>TRADE-OFFS E TENSÕES INERENTES</t>
         </is>
       </c>
-      <c r="B76" s="16" t="inlineStr">
+      <c r="B76" s="35" t="inlineStr">
         <is>
           <t>Sacrifício da completude para reduzir ruído</t>
         </is>
       </c>
       <c r="C76" s="4" t="n"/>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="D76" s="35" t="inlineStr">
         <is>
           <t>“Trying to keep every single messy record just to maximize completeness usually introduces too much noise.”</t>
         </is>
       </c>
-      <c r="E76" s="16" t="inlineStr">
+      <c r="E76" s="35" t="inlineStr">
         <is>
           <t>Balancing data quality in real-world machine learning projects is essentially a constant game of trade-offs, as you can rarely optimize for everything at once. For instance, highly accurate models demand massive amounts of computing power, so you often have to settle for a slightly less precise but much faster model just to make it practical to run in production. Similarly, while neatly organized and highly structured databases are great for developers to read and understand, they are notoriously slow for training, meaning we usually end up flattening the data into ugly, denormalized tables so the algorithms can ingest them efficiently. Even when building the dataset itself, trying to keep every single messy record just to maximize completeness usually introduces too much noise, making it far better to simply throw out the bad data and accept a smaller dataset in exchange for a much more accurate and reliable model.</t>
         </is>
